--- a/public/sales-report-template.xlsx
+++ b/public/sales-report-template.xlsx
@@ -213,7 +213,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Türkçe'!B11</f>
+              <f>'Türkçe'!B46</f>
             </strRef>
           </tx>
           <spPr>
@@ -229,12 +229,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Türkçe'!$A$12:$A$35</f>
+              <f>'Türkçe'!$A$47:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Türkçe'!$B$12:$B$35</f>
+              <f>'Türkçe'!$B$47:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -249,21 +249,6 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Saat</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -302,7 +287,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -314,7 +299,121 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>En çok satan ürünler</a:t>
+              <a:t>الدخل حسب الساعة</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'العربية'!C46</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="32000">
+              <a:solidFill>
+                <a:srgbClr val="1E9E6A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC93C"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="0E1630"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'العربية'!$A$47:$A$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'العربية'!$C$47:$C$70</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>الدخل</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0 &quot;₺&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>المنتجات الأكثر مبيعًا (الكمية)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -329,7 +428,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Türkçe'!B38</f>
+              <f>'العربية'!B73</f>
             </strRef>
           </tx>
           <spPr>
@@ -345,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Türkçe'!$A$39:$A$78</f>
+              <f>'العربية'!$A$74:$A$113</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Türkçe'!$B$39:$B$78</f>
+              <f>'العربية'!$B$74:$B$113</f>
             </numRef>
           </val>
         </ser>
@@ -388,7 +487,381 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>الدخل حسب المنتج</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'العربية'!C73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1E9E6A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E1630"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'العربية'!$A$74:$A$113</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'العربية'!$C$74:$C$113</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0 &quot;₺&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Saatlere göre gelir</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Türkçe'!C46</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="32000">
+              <a:solidFill>
+                <a:srgbClr val="1E9E6A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC93C"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="0E1630"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Türkçe'!$A$47:$A$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Türkçe'!$C$47:$C$70</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Gelir</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0 &quot;₺&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>En çok satan ürünler (adet)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Türkçe'!B73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FFC93C"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E1630"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Türkçe'!$A$74:$A$113</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Türkçe'!$B$74:$B$113</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Ürünlere göre gelir</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Türkçe'!C73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1E9E6A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E1630"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Türkçe'!$A$74:$A$113</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Türkçe'!$C$74:$C$113</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0 &quot;₺&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -415,7 +888,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'English'!B11</f>
+              <f>'English'!B46</f>
             </strRef>
           </tx>
           <spPr>
@@ -431,12 +904,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'English'!$A$12:$A$35</f>
+              <f>'English'!$A$47:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'English'!$B$12:$B$35</f>
+              <f>'English'!$B$47:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -451,21 +924,6 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Hour</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -504,7 +962,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -516,7 +974,121 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Best-selling items</a:t>
+              <a:t>Income by hour</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'English'!C46</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="32000">
+              <a:solidFill>
+                <a:srgbClr val="1E9E6A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC93C"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="0E1630"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'English'!$A$47:$A$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'English'!$C$47:$C$70</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Income</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0 &quot;₺&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Best-selling items (qty)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -531,7 +1103,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'English'!B38</f>
+              <f>'English'!B73</f>
             </strRef>
           </tx>
           <spPr>
@@ -547,12 +1119,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'English'!$A$39:$A$78</f>
+              <f>'English'!$A$74:$A$113</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'English'!$B$39:$B$78</f>
+              <f>'English'!$B$74:$B$113</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +1162,94 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Income by item</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'English'!C73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1E9E6A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E1630"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'English'!$A$74:$A$113</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'English'!$C$74:$C$113</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0 &quot;₺&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -617,7 +1276,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'العربية'!B11</f>
+              <f>'العربية'!B46</f>
             </strRef>
           </tx>
           <spPr>
@@ -633,12 +1292,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'العربية'!$A$12:$A$35</f>
+              <f>'العربية'!$A$47:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'العربية'!$B$12:$B$35</f>
+              <f>'العربية'!$B$47:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -653,21 +1312,6 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>الساعة</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -706,102 +1350,21 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>المنتجات الأكثر مبيعًا</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'العربية'!B38</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC93C"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="0E1630"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'العربية'!$A$39:$A$78</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'العربية'!$B$39:$B$78</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="50"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+  <twoCellAnchor>
     <from>
-      <col>4</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3060000"/>
+    <to>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -815,15 +1378,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor>
     <from>
-      <col>14</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3060000"/>
+    <to>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -837,20 +1405,79 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+  <twoCellAnchor>
     <from>
-      <col>4</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3060000"/>
+    <to>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -864,15 +1491,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor>
     <from>
-      <col>14</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3060000"/>
+    <to>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -886,20 +1518,79 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+  <twoCellAnchor>
     <from>
-      <col>4</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3060000"/>
+    <to>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -913,15 +1604,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor>
     <from>
-      <col>14</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3060000"/>
+    <to>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -935,7 +1631,61 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -1228,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1266,7 +2016,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>SUM(C12:C35)</f>
+        <f>SUM(C47:C70)</f>
         <v/>
       </c>
     </row>
@@ -1277,7 +2027,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>SUM(B12:B35)</f>
+        <f>SUM(B47:B70)</f>
         <v/>
       </c>
     </row>
@@ -1305,537 +2055,369 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Grafikler</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>Saatlik satışlar</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Saat</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Sipariş</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Gelir</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>04:00</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="B55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="B58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="B63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="B67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="B70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Satılan ürünler</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>Ürün</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Adet</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Gelir</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="9" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n"/>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n"/>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n"/>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n"/>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="9" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="9" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="9" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n"/>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="9" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n"/>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="9" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="9" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="9" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n"/>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="9" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="9" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="9" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="9" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -1861,6 +2443,181 @@
       <c r="A78" s="3" t="n"/>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n"/>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n"/>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1879,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1917,7 +2674,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>SUM(C12:C35)</f>
+        <f>SUM(C47:C70)</f>
         <v/>
       </c>
     </row>
@@ -1928,7 +2685,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>SUM(B12:B35)</f>
+        <f>SUM(B47:B70)</f>
         <v/>
       </c>
     </row>
@@ -1956,537 +2713,369 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Charts</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>Sales by hour</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>04:00</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="B55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="B58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="B63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="B67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="B70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Items sold</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="9" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n"/>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n"/>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n"/>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n"/>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="9" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="9" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="9" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n"/>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="9" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n"/>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="9" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="9" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="9" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n"/>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="9" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="9" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="9" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="9" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -2512,6 +3101,181 @@
       <c r="A78" s="3" t="n"/>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n"/>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n"/>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2530,7 +3294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2568,7 +3332,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>SUM(C12:C35)</f>
+        <f>SUM(C47:C70)</f>
         <v/>
       </c>
     </row>
@@ -2579,7 +3343,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>SUM(B12:B35)</f>
+        <f>SUM(B47:B70)</f>
         <v/>
       </c>
     </row>
@@ -2607,537 +3371,369 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>الرسوم البيانية</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>المبيعات حسب الساعة</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>الساعة</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>الطلبات</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>الدخل</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="B47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>04:00</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="B55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="B58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="B63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="B67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="B70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>المنتجات المباعة</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>المنتج</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>الكمية</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>الدخل</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="9" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n"/>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n"/>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n"/>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n"/>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="9" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="9" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="9" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n"/>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="9" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n"/>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="9" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="9" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="9" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n"/>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="9" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="9" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="9" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="9" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -3163,6 +3759,181 @@
       <c r="A78" s="3" t="n"/>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n"/>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n"/>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/sales-report-template.xlsx
+++ b/public/sales-report-template.xlsx
@@ -349,6 +349,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -545,6 +546,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -724,6 +726,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -882,6 +885,7 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -920,6 +924,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1078,6 +1083,7 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1116,6 +1122,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -1295,6 +1302,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1453,6 +1461,7 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1491,6 +1500,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1649,6 +1659,7 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1687,6 +1698,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1883,6 +1895,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -2062,6 +2075,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2220,6 +2234,7 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -2258,6 +2273,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2416,6 +2432,7 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -2454,6 +2471,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
